--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -31,10 +31,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="135">
   <si>
-    <t>Wycena NK6501 · ul. Ogrodowa 8, Warszawa</t>
-  </si>
-  <si>
-    <t>Wygenerowano 21.10.2026, 09:16:59 · ceny netto w zł · szablon NK6501</t>
+    <t>KALKULACJA NK6501</t>
+  </si>
+  <si>
+    <t>Data kalkulacji</t>
+  </si>
+  <si>
+    <t>ul. Ogrodowa 8, Warszawa</t>
+  </si>
+  <si>
+    <t>21.10.2026</t>
+  </si>
+  <si>
+    <t>Poza Krakowem · 300 km od Krakowa · Wygenerowano 21.10.2026, 18:59:05 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>
@@ -52,16 +61,16 @@
     <t>Próg opłacalności · zysk 0%</t>
   </si>
   <si>
-    <t>Montaż / konserwacja roczna</t>
-  </si>
-  <si>
-    <t>3 tyg. / 3600 zł</t>
+    <t>Czas montażu</t>
+  </si>
+  <si>
+    <t>3 tyg.</t>
   </si>
   <si>
     <t>maks. rabat −17 845 zł (−12,45%)</t>
   </si>
   <si>
-    <t>12 dni pracy, ekipa 4 os.; konserwacja 50 zł/MP/mies.</t>
+    <t>12 dni pracy, ekipa 4 os.</t>
   </si>
   <si>
     <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
@@ -88,6 +97,75 @@
     <t>Zielone: rabat bez zejścia poniżej zysku 10%. Żółte: poniżej zysku do porównania. Przy zysku 0% w cenie zostają koszty, KOB, GDW i podatek.</t>
   </si>
   <si>
+    <t>Dane wejściowe</t>
+  </si>
+  <si>
+    <t>ZAKRES</t>
+  </si>
+  <si>
+    <t>WYMIARY</t>
+  </si>
+  <si>
+    <t>Urządzenia</t>
+  </si>
+  <si>
+    <t>Prześwit</t>
+  </si>
+  <si>
+    <t>6× NK6501</t>
+  </si>
+  <si>
+    <t>215 cm</t>
+  </si>
+  <si>
+    <t>6 urządzeń = 6 miejsc postojowych</t>
+  </si>
+  <si>
+    <t>Wysokość pojazdów</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>▲ 200 cm   ▼ – cm</t>
+  </si>
+  <si>
+    <t>Opis wariantu</t>
+  </si>
+  <si>
+    <t>P-215 | Hpoj. G-200</t>
+  </si>
+  <si>
+    <t>Lokalizacja</t>
+  </si>
+  <si>
+    <t>Montaż</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Poza Krakowem · 300 km od Krakowa</t>
+  </si>
+  <si>
+    <t>3 tyg. (12 dni pracy), ekipa 4 os.</t>
+  </si>
+  <si>
+    <t>1 TIR × 3500 zł</t>
+  </si>
+  <si>
+    <t>Konserwacja · wariant 1 · 50 zł/MP/mies.</t>
+  </si>
+  <si>
+    <t>Konserwacja · wariant 2 · 60 zł/MP/mies.</t>
+  </si>
+  <si>
+    <t>300 zł miesięcznie</t>
+  </si>
+  <si>
+    <t>360 zł miesięcznie</t>
+  </si>
+  <si>
     <t>Warianty wykonania</t>
   </si>
   <si>
@@ -166,46 +244,7 @@
     <t>Osobodni razem</t>
   </si>
   <si>
-    <t>Dane wejściowe</t>
-  </si>
-  <si>
-    <t>Inwestycja</t>
-  </si>
-  <si>
-    <t>Nazwa / adres</t>
-  </si>
-  <si>
-    <t>ul. Ogrodowa 8, Warszawa</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>2026-10-21</t>
-  </si>
-  <si>
-    <t>Opis / wariant</t>
-  </si>
-  <si>
-    <t>P-215 | Hpoj. G-200</t>
-  </si>
-  <si>
-    <t>Prześwit</t>
-  </si>
-  <si>
-    <t>215 cm</t>
-  </si>
-  <si>
-    <t>Wysokość pojazdów ▲ / ▼</t>
-  </si>
-  <si>
-    <t>200 / – cm</t>
-  </si>
-  <si>
-    <t>Lokalizacja</t>
-  </si>
-  <si>
-    <t>Poza Krakowem, 300 km od Krakowa</t>
+    <t>Pozostałe dane wejściowe</t>
   </si>
   <si>
     <t>Km pomiary / montaż</t>
@@ -214,18 +253,12 @@
     <t>300 / 350 km</t>
   </si>
   <si>
-    <t>Urządzenia</t>
-  </si>
-  <si>
     <t>Szablon urządzenia</t>
   </si>
   <si>
     <t>NK6501</t>
   </si>
   <si>
-    <t>6 × Palety NK6501 = 6 MP</t>
-  </si>
-  <si>
     <t>Sterowanie palet (Mufas)</t>
   </si>
   <si>
@@ -238,42 +271,18 @@
     <t>2 osd (auto 0, ręcznie 2)</t>
   </si>
   <si>
-    <t>Montaż i transport</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
-    <t>1 TIR × 3500 zł</t>
-  </si>
-  <si>
     <t>Rozładunek sprzętu</t>
   </si>
   <si>
     <t>3000 zł jednorazowo, 0,5 dni rozładunku</t>
   </si>
   <si>
-    <t>Ekipa</t>
-  </si>
-  <si>
-    <t>4 os., średnio 375 zł/dzień</t>
-  </si>
-  <si>
-    <t>Czas montażu</t>
-  </si>
-  <si>
-    <t>12 dni pracy = 3 tyg.</t>
-  </si>
-  <si>
     <t>Czas podróży</t>
   </si>
   <si>
     <t>stary wzór (poprawiony)</t>
   </si>
   <si>
-    <t>Narzuty i serwis</t>
-  </si>
-  <si>
     <t>11% oraz 10% do porównania</t>
   </si>
   <si>
@@ -283,12 +292,6 @@
     <t>4.325 / 3.86</t>
   </si>
   <si>
-    <t>Konserwacja</t>
-  </si>
-  <si>
-    <t>50 zł/MP/mies.: 3600 zł rocznie; 60 zł/MP/mies.: 4320 zł rocznie</t>
-  </si>
-  <si>
     <t>Obliczenia krok po kroku</t>
   </si>
   <si>
@@ -364,9 +367,6 @@
     <t>Dojazdy, ludzie</t>
   </si>
   <si>
-    <t>Montaż</t>
-  </si>
-  <si>
     <t>Diety</t>
   </si>
   <si>
@@ -397,9 +397,6 @@
     <t>Pomarańczowe = zmienione względem domyślnego NK38</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Pozycje kosztowe</t>
   </si>
   <si>
@@ -431,6 +428,9 @@
   </si>
   <si>
     <t>Zestawienie do oferty</t>
+  </si>
+  <si>
+    <t>Wygenerowano 21.10.2026, 18:59:05 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>PRZYKŁAD – ul. Ogrodowa 8, Warszawa</t>
@@ -440,17 +440,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;zł&quot;;-#,##0 &quot;zł&quot;;&quot;–&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%&quot;  oferta&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;-0.0%;&quot;–&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0%&quot;  do porównania&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%&quot;&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%&quot;  próg&quot;"/>
-    <numFmt numFmtId="170" formatCode="#,##0 &quot;€&quot;"/>
-    <numFmt numFmtId="171" formatCode="#,##0.##"/>
+    <numFmt numFmtId="170" formatCode="#,##0 &quot;zł rocznie&quot;"/>
+    <numFmt numFmtId="171" formatCode="#,##0 &quot;€&quot;"/>
+    <numFmt numFmtId="172" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -459,9 +460,20 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FFC4E4E7"/>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="15"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -522,6 +534,29 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0E171C"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF0E171C"/>
+      <sz val="9.5"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF0E171C"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -535,11 +570,6 @@
       <color rgb="FF0E171C"/>
       <sz val="8.5"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
-      <sz val="9.5"/>
-      <name val="Consolas"/>
     </font>
   </fonts>
   <fills count="9">
@@ -585,7 +615,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -657,6 +687,15 @@
     <border>
       <left/>
       <right/>
+      <top style="medium">
+        <color rgb="FF0A6B74"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="thin">
         <color rgb="FFD3D9DD"/>
@@ -667,132 +706,171 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1133,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1142,809 +1220,805 @@
     <col min="5" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
         <v>143372.21160465115</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7">
         <v>141563.51422988507</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>125527.64059793815</v>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>125527.64059793815</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="B14" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="C14" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>0.11</v>
-      </c>
-      <c r="B14" s="12">
-        <v>143372.21160465115</v>
-      </c>
-      <c r="C14" s="12">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13">
-        <v>0</v>
-      </c>
-      <c r="E14" s="12">
-        <v>18645.791860465117</v>
-      </c>
-      <c r="F14" s="12">
-        <v>23895.368600775193</v>
+      <c r="D14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B15" s="15">
-        <v>141563.51422988507</v>
+        <v>143372.21160465115</v>
       </c>
       <c r="C15" s="15">
-        <v>-1808.6973747660813</v>
+        <v>0</v>
       </c>
       <c r="D15" s="16">
-        <v>-0.01261539704607169</v>
+        <v>0</v>
       </c>
       <c r="E15" s="15">
-        <v>17066.178160919542</v>
+        <v>18645.791860465117</v>
       </c>
       <c r="F15" s="15">
-        <v>23593.91903831418</v>
+        <v>23895.368600775193</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="B16" s="18">
+        <v>141563.51422988507</v>
+      </c>
+      <c r="C16" s="18">
+        <v>-1808.6973747660813</v>
+      </c>
+      <c r="D16" s="19">
+        <v>-0.01261539704607169</v>
+      </c>
+      <c r="E16" s="18">
+        <v>17066.178160919542</v>
+      </c>
+      <c r="F16" s="18">
+        <v>23593.91903831418</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="20">
         <v>0.08</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B17" s="21">
         <v>138068.05413483147</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C17" s="21">
         <v>-5304.157469819678</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D17" s="22">
         <v>-0.036995714932862245</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E17" s="21">
         <v>14013.441573033711</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F17" s="21">
         <v>23011.342355805245</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="20">
         <v>0.06</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B18" s="21">
         <v>134726.24063736264</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C18" s="21">
         <v>-8645.970967288507</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D18" s="22">
         <v>-0.06030437049495875</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E18" s="21">
         <v>11094.891208791207</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F18" s="21">
         <v>22454.37343956044</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="17">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="20">
         <v>0.04</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B19" s="21">
         <v>131528.16105376347</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C19" s="21">
         <v>-11844.050550887681</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D19" s="22">
         <v>-0.08261050323717994</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E19" s="21">
         <v>8301.86989247312</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F19" s="21">
         <v>21921.360175627244</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
-        <v>0.02</v>
-      </c>
-      <c r="B19" s="18">
-        <v>128464.73745263158</v>
-      </c>
-      <c r="C19" s="18">
-        <v>-14907.474152019568</v>
-      </c>
-      <c r="D19" s="19">
-        <v>-0.1039774303902553</v>
-      </c>
-      <c r="E19" s="18">
-        <v>5626.449473684211</v>
-      </c>
-      <c r="F19" s="18">
-        <v>21410.789575438597</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="B20" s="21">
+        <v>128464.73745263158</v>
+      </c>
+      <c r="C20" s="21">
+        <v>-14907.474152019568</v>
+      </c>
+      <c r="D20" s="22">
+        <v>-0.1039774303902553</v>
+      </c>
+      <c r="E20" s="21">
+        <v>5626.449473684211</v>
+      </c>
+      <c r="F20" s="21">
+        <v>21410.789575438597</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="23">
         <v>0</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B21" s="24">
         <v>125527.64059793815</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C21" s="24">
         <v>-17844.571006713</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D21" s="25">
         <v>-0.1244632471452655</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E21" s="24">
         <v>3061.3556701030934</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F21" s="24">
         <v>20921.273432989692</v>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="10" t="s">
+    <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="25">
-        <v>143372.21160465115</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="25">
-        <v>141563.51422988507</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="27">
-        <v>23895.368600775193</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+    </row>
+    <row r="26" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="29">
-        <v>23593.91903831418</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="26" t="s">
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="30">
-        <v>5524.940716942241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+    </row>
+    <row r="27" ht="21" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="31">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+    </row>
+    <row r="28" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-    </row>
-    <row r="34" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+    </row>
+    <row r="29" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="30" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="27">
-        <v>3554.302325581395</v>
-      </c>
-      <c r="C35" s="27">
-        <v>3508.6206896551726</v>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="35"/>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="36"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="37">
+        <v>3600</v>
+      </c>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37">
+        <v>4320</v>
+      </c>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+    </row>
+    <row r="37" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
+      <c r="D37" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="27">
+    <row r="39" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="40" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="39">
+        <v>143372.21160465115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="39">
+        <v>141563.51422988507</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="41">
+        <v>23895.368600775193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="43">
+        <v>23593.91903831418</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="44">
+        <v>5524.940716942241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+    </row>
+    <row r="50" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="41">
+        <v>3554.302325581395</v>
+      </c>
+      <c r="C51" s="41">
+        <v>3508.6206896551726</v>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+    </row>
+    <row r="54" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="41">
         <v>82900</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="29">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="27">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="41">
         <v>6500</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="29">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="43">
         <v>16867.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="27">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="41">
         <v>12513.1</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="29">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="43">
         <v>5945.819744186047</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="27">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="41">
         <v>18645.791860465117</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="29">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="43">
         <v>17066.178160919542</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="39">
         <v>124726.41974418603</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" s="33">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="47">
         <v>44.980000000000004</v>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="34"/>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C52" s="36"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="36"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B54" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C54" s="36"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B55" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="C56" s="36"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="36"/>
-      <c r="D57" s="36"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="36"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" s="36"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-    </row>
-    <row r="59" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60" s="34"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="B61" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" s="36"/>
-      <c r="D62" s="36"/>
-      <c r="E62" s="36"/>
-      <c r="F62" s="36"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="B63" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C63" s="36"/>
-      <c r="D63" s="36"/>
-      <c r="E63" s="36"/>
-      <c r="F63" s="36"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="B64" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="C64" s="36"/>
-      <c r="D64" s="36"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="36"/>
-    </row>
-    <row r="65" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="34"/>
-      <c r="C66" s="34"/>
-      <c r="D66" s="34"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="34"/>
+    <row r="66" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
-      <c r="E67" s="36"/>
-      <c r="F67" s="36"/>
+      <c r="A67" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" s="49"/>
+      <c r="D67" s="49"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
+      <c r="A68" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" s="49"/>
+      <c r="D68" s="49"/>
+      <c r="E68" s="49"/>
+      <c r="F68" s="49"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="B69" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
+      <c r="A69" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="C69" s="49"/>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
+      <c r="A70" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70" s="49"/>
+      <c r="D70" s="49"/>
+      <c r="E70" s="49"/>
+      <c r="F70" s="49"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="36"/>
-    </row>
-    <row r="72" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A71" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" s="49"/>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="C72" s="49"/>
+      <c r="D72" s="49"/>
+      <c r="E72" s="49"/>
+      <c r="F72" s="49"/>
+    </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="34"/>
-      <c r="C73" s="34"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="34"/>
-      <c r="F73" s="34"/>
+      <c r="A73" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" s="49"/>
+      <c r="D73" s="49"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="49"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B74" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C74" s="36"/>
-      <c r="D74" s="36"/>
-      <c r="E74" s="36"/>
-      <c r="F74" s="36"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="B75" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" s="36"/>
-      <c r="D75" s="36"/>
-      <c r="E75" s="36"/>
-      <c r="F75" s="36"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="B76" s="36" t="s">
+      <c r="A74" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="C76" s="36"/>
-      <c r="D76" s="36"/>
-      <c r="E76" s="36"/>
-      <c r="F76" s="36"/>
-    </row>
-    <row r="77" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B74" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" s="49"/>
+      <c r="D74" s="49"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+    </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
+  <mergeCells count="55">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="D10:F10"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A53:F53"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B71:F71"/>
-    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B73:F73"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B76:F76"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
@@ -1952,7 +2026,7 @@
     <oddFooter>&amp;L&amp;8ul. Ogrodowa 8, Warszawa&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="36" max="16838" man="1"/>
+    <brk id="38" max="16838" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1967,387 +2041,387 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="A1" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="A2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="A4" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="36" t="s">
+      <c r="A5" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
+      <c r="B5" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
+      <c r="B6" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
+      <c r="A7" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="36" t="s">
+      <c r="A8" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
+      <c r="B8" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="36" t="s">
+      <c r="A9" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
+      <c r="B9" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="A11" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>21</v>
+      <c r="A12" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="37">
+      <c r="A13" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="51">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" s="31">
+      <c r="A14" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="45">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="37">
+      <c r="A15" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="51">
         <v>15.98</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" s="31">
+      <c r="A16" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="45">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="32">
+      <c r="A17" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="46">
         <v>3300</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="31">
+      <c r="A18" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="45">
         <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="27">
+      <c r="A19" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="41">
         <v>82900</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="A20" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="43">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" s="27">
+      <c r="A21" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="41">
         <v>3729</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="43">
         <v>6760</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="27">
+      <c r="A23" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="41">
         <v>3500</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="43">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="27">
+      <c r="A25" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="41">
         <v>3000</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26" s="29">
+      <c r="A26" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="43">
         <v>750</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="27">
+      <c r="A27" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="41">
         <v>5242.5</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="B28" s="29">
+      <c r="A28" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="43">
         <v>10875</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="41">
         <v>2024.1000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="39">
         <v>118780.6</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="41">
         <v>690.5848837209303</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="43">
         <v>3452.9244186046512</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="41">
         <v>15192.867441860466</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="43">
         <v>18645.791860465117</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="41">
         <v>5255.234860465116</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="39">
         <v>143372.21160465115</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="B41" s="39" t="s">
+      <c r="A41" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="D41" s="52"/>
+      <c r="E41" s="53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="38"/>
-      <c r="E41" s="39" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="40" t="s">
+      <c r="B42" s="55">
+        <v>130</v>
+      </c>
+      <c r="C42" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="54"/>
+      <c r="E42" s="56" t="s">
         <v>124</v>
       </c>
-      <c r="B42" s="41">
+    </row>
+    <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="55">
+        <v>45</v>
+      </c>
+      <c r="C43" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" s="54"/>
+      <c r="E43" s="56" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" s="54"/>
+      <c r="E44" s="56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="C42" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="D42" s="40"/>
-      <c r="E42" s="42" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="B43" s="41">
-        <v>45</v>
-      </c>
-      <c r="C43" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="D43" s="40"/>
-      <c r="E43" s="42" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="B44" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="C44" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="D44" s="40"/>
-      <c r="E44" s="42" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="40" t="s">
+      <c r="B45" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="B45" s="42" t="s">
-        <v>132</v>
-      </c>
       <c r="C45" t="s">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="D45"/>
       <c r="E45" t="s">
-        <v>122</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2391,22 +2465,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="50"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="5"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="43"/>
+      <c r="B4" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 21.10.2026, 19:14:00 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 21.10.2026, 19:25:59 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 21.10.2026, 19:25:59 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 22.10.2026, 08:15:57 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 22.10.2026, 08:15:57 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 22.10.2026, 08:47:04 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 22.10.2026, 08:47:04 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 23.10.2026, 05:42:40 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 23.10.2026, 05:42:40 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 23.10.2026, 06:31:44 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 23.10.2026, 06:31:44 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 23.10.2026, 06:32:56 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 23.10.2026, 06:32:56 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 27.10.2026, 12:24:44 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 12:24:44 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 27.10.2026, 14:03:05 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:03:05 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 27.10.2026, 14:04:44 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>
@@ -105,7 +105,7 @@
     <t>6× NK6501</t>
   </si>
   <si>
-    <t>215 cm</t>
+    <t>P 215 cm</t>
   </si>
   <si>
     <t>Razem</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="134">
   <si>
     <t>KALKULACJA NK6501</t>
   </si>
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:04:44 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 27.10.2026, 14:13:52 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>
@@ -120,6 +120,15 @@
     <t>▲ 200 cm    ▼ – cm</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>KOB / GDW</t>
+  </si>
+  <si>
+    <t>0,5% / 2,5%</t>
+  </si>
+  <si>
     <t>Opis wariantu</t>
   </si>
   <si>
@@ -157,9 +166,6 @@
   </si>
   <si>
     <t>Malowanie RAL</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Konserwacja · wariant 1 · 6 MP</t>
@@ -1228,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1563,166 +1569,166 @@
       <c r="E25" s="29"/>
       <c r="F25" s="29"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+    <row r="26" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="32" t="s">
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32" t="s">
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32" t="s">
+      <c r="B29" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="32"/>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="33" t="s">
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33" t="s">
+      <c r="B30" s="32"/>
+      <c r="C30" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33" t="s">
+      <c r="D30" s="32"/>
+      <c r="E30" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="33"/>
-    </row>
-    <row r="31" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="F30" s="32"/>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="33"/>
+      <c r="C31" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="12" t="s">
+      <c r="D31" s="33"/>
+      <c r="E31" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="33"/>
+    </row>
+    <row r="33" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="34" t="s">
+      <c r="B33" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="36">
+      <c r="F33" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="36">
         <v>3554.302325581395</v>
       </c>
-      <c r="F32" s="36">
+      <c r="F34" s="36">
         <v>3508.6206896551726</v>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="38" t="s">
+    <row r="36" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38" t="s">
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-    </row>
-    <row r="36" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="39" t="s">
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39" t="s">
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="40" t="s">
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+    </row>
+    <row r="38" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="40"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40" t="s">
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-    </row>
-    <row r="39" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="41" t="s">
+      <c r="B39" s="40"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="42" t="s">
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+    </row>
+    <row r="41" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B42" s="42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C42" s="42"/>
       <c r="D42" s="42"/>
@@ -1731,10 +1737,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="41" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B43" s="42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C43" s="42"/>
       <c r="D43" s="42"/>
@@ -1743,18 +1749,42 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="41" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B44" s="42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C44" s="42"/>
       <c r="D44" s="42"/>
       <c r="E44" s="42"/>
       <c r="F44" s="42"/>
     </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="42"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+    </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="54">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -1782,29 +1812,33 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="D37:F37"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
@@ -1825,7 +1859,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -1834,7 +1868,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1843,7 +1877,7 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1852,10 +1886,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
@@ -1863,10 +1897,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
@@ -1874,10 +1908,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -1885,10 +1919,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -1896,10 +1930,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="41" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -1907,7 +1941,7 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -1916,23 +1950,23 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C12" s="44"/>
       <c r="D12" s="44"/>
       <c r="E12" s="45" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="46" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C13" s="47"/>
       <c r="D13" s="47"/>
@@ -1942,10 +1976,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="49" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" s="50"/>
       <c r="D14" s="50"/>
@@ -1955,10 +1989,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C15" s="47"/>
       <c r="D15" s="47"/>
@@ -1968,10 +2002,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="49" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C16" s="50"/>
       <c r="D16" s="50"/>
@@ -1981,10 +2015,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C17" s="47"/>
       <c r="D17" s="47"/>
@@ -1994,10 +2028,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C18" s="50"/>
       <c r="D18" s="50"/>
@@ -2010,7 +2044,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C19" s="47"/>
       <c r="D19" s="47"/>
@@ -2020,10 +2054,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="49" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C20" s="50"/>
       <c r="D20" s="50"/>
@@ -2033,10 +2067,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="46" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="47"/>
@@ -2046,10 +2080,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="49" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C22" s="50"/>
       <c r="D22" s="50"/>
@@ -2059,10 +2093,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C23" s="47"/>
       <c r="D23" s="47"/>
@@ -2072,10 +2106,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="49" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C24" s="50"/>
       <c r="D24" s="50"/>
@@ -2085,10 +2119,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="46" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -2098,10 +2132,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C26" s="50"/>
       <c r="D26" s="50"/>
@@ -2111,10 +2145,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -2124,10 +2158,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="55" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
@@ -2137,10 +2171,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="46" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C29" s="47"/>
       <c r="D29" s="47"/>
@@ -2150,10 +2184,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="49" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C30" s="50"/>
       <c r="D30" s="50"/>
@@ -2163,10 +2197,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="46" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C31" s="47"/>
       <c r="D31" s="47"/>
@@ -2176,10 +2210,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="49" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C32" s="50"/>
       <c r="D32" s="50"/>
@@ -2189,10 +2223,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="46" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C33" s="47"/>
       <c r="D33" s="47"/>
@@ -2202,10 +2236,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
@@ -2215,10 +2249,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="55" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
@@ -2228,7 +2262,7 @@
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B36" s="43"/>
       <c r="C36" s="43"/>
@@ -2237,7 +2271,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2246,77 +2280,77 @@
     </row>
     <row r="39" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="58" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B39" s="59" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C39" s="58" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D39" s="58"/>
       <c r="E39" s="59" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="60" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B40" s="61">
         <v>130</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D40" s="60"/>
       <c r="E40" s="62" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="60" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B41" s="61">
         <v>45</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D41" s="60"/>
       <c r="E41" s="62" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="58" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C42" s="60" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D42" s="60"/>
       <c r="E42" s="62" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="60" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B43" s="62" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D43"/>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:13:52 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 27.10.2026, 14:16:58 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>
@@ -270,25 +270,25 @@
     <t>Kwota</t>
   </si>
   <si>
-    <t>Osobodni montażu (F50)</t>
+    <t>Osobodni montażu</t>
   </si>
   <si>
     <t>z cennika osobodni na urządzenie + utrudnienia</t>
   </si>
   <si>
-    <t>Tygodnie / dni montażu (B55)</t>
+    <t>Tygodnie / dni montażu</t>
   </si>
   <si>
     <t>tygodniowe wyjazdy ekipy</t>
   </si>
   <si>
-    <t>Osobodni podróży i rozładunku (G59)</t>
+    <t>Osobodni podróży i rozładunku</t>
   </si>
   <si>
     <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
   </si>
   <si>
-    <t>Dni pracy ekipy (J39)</t>
+    <t>Dni pracy ekipy</t>
   </si>
   <si>
     <t>(osd montażu + podróży) ÷ 4 os.</t>
@@ -384,7 +384,7 @@
     <t>14% od robocizny (18 892 zł) i zysku z narzutem</t>
   </si>
   <si>
-    <t>Cena kontraktu, zysk 11% (K39)</t>
+    <t>Cena kontraktu, zysk 11%</t>
   </si>
   <si>
     <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:16:58 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 27.10.2026, 14:20:06 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:20:06 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 27.10.2026, 14:21:22 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:21:22 · ceny netto w zł · szablon NK6501</t>
+    <t>Wygenerowano 27.10.2026, 14:28:47 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 11%</t>
@@ -54,13 +54,13 @@
     <t>Próg opłacalności · zysk 0%</t>
   </si>
   <si>
-    <t>23 895 zł / MP · 5525 € / MP</t>
-  </si>
-  <si>
-    <t>rabat −1809 zł (−1,26%)</t>
-  </si>
-  <si>
-    <t>maks. rabat −17 845 zł (−12,45%)</t>
+    <t>23 956 zł / MP · 5539 € / MP</t>
+  </si>
+  <si>
+    <t>rabat −1817 zł (−1,26%)</t>
+  </si>
+  <si>
+    <t>maks. rabat −17 923 zł (−12,47%)</t>
   </si>
   <si>
     <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
@@ -126,7 +126,7 @@
     <t>KOB / GDW</t>
   </si>
   <si>
-    <t>0,5% / 2,5%</t>
+    <t>0,52% / 2,69%</t>
   </si>
   <si>
     <t>Opis wariantu</t>
@@ -357,13 +357,13 @@
     <t>KOB</t>
   </si>
   <si>
-    <t>0,5% ceny przed podatkiem (138 117 zł)</t>
+    <t>0,52% ceny przed podatkiem (138 439 zł)</t>
   </si>
   <si>
     <t>GDW</t>
   </si>
   <si>
-    <t>2,5% ceny przed podatkiem</t>
+    <t>2,69% ceny przed podatkiem</t>
   </si>
   <si>
     <t>Zysk 11%</t>
@@ -375,7 +375,7 @@
     <t>Zysk z narzutem (zysk + GDW)</t>
   </si>
   <si>
-    <t>zysk 11% + GDW 2,5%</t>
+    <t>zysk 11% + GDW 2,69%</t>
   </si>
   <si>
     <t>Podatek</t>
@@ -1293,15 +1293,15 @@
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>143372.21160465115</v>
+        <v>143736.10315547785</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7">
-        <v>141563.51422988507</v>
+        <v>141919.0459762673</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="8">
-        <v>125527.64059793815</v>
+        <v>125813.31188780992</v>
       </c>
       <c r="F6" s="8"/>
     </row>
@@ -1354,7 +1354,7 @@
         <v>0.11</v>
       </c>
       <c r="B11" s="14">
-        <v>143372.21160465115</v>
+        <v>143736.10315547785</v>
       </c>
       <c r="C11" s="14">
         <v>0</v>
@@ -1363,10 +1363,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="14">
-        <v>18645.791860465117</v>
+        <v>18945.36726107226</v>
       </c>
       <c r="F11" s="14">
-        <v>23895.368600775193</v>
+        <v>23956.017192579642</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1374,19 +1374,19 @@
         <v>0.1</v>
       </c>
       <c r="B12" s="17">
-        <v>141563.51422988507</v>
+        <v>141919.0459762673</v>
       </c>
       <c r="C12" s="17">
-        <v>-1808.6973747660813</v>
+        <v>-1817.057179210533</v>
       </c>
       <c r="D12" s="18">
-        <v>-0.01261539704607169</v>
+        <v>-0.012641619880601892</v>
       </c>
       <c r="E12" s="17">
-        <v>17066.178160919542</v>
+        <v>17358.66256912443</v>
       </c>
       <c r="F12" s="17">
-        <v>23593.91903831418</v>
+        <v>23653.174329377885</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1394,19 +1394,19 @@
         <v>0.08</v>
       </c>
       <c r="B13" s="20">
-        <v>138068.05413483147</v>
+        <v>138407.70575157658</v>
       </c>
       <c r="C13" s="20">
-        <v>-5304.157469819678</v>
+        <v>-5328.397403901268</v>
       </c>
       <c r="D13" s="21">
-        <v>-0.036995714932862245</v>
+        <v>-0.03707069613636037</v>
       </c>
       <c r="E13" s="20">
-        <v>14013.441573033711</v>
+        <v>14292.462961711713</v>
       </c>
       <c r="F13" s="20">
-        <v>23011.342355805245</v>
+        <v>23067.950958596095</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1414,19 +1414,19 @@
         <v>0.06</v>
       </c>
       <c r="B14" s="20">
-        <v>134726.24063736264</v>
+        <v>135051.05011828194</v>
       </c>
       <c r="C14" s="20">
-        <v>-8645.970967288507</v>
+        <v>-8685.053037195903</v>
       </c>
       <c r="D14" s="21">
-        <v>-0.06030437049495875</v>
+        <v>-0.06042360163195305</v>
       </c>
       <c r="E14" s="20">
-        <v>11094.891208791207</v>
+        <v>11361.338226872247</v>
       </c>
       <c r="F14" s="20">
-        <v>22454.37343956044</v>
+        <v>22508.50835304699</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1434,19 +1434,19 @@
         <v>0.04</v>
       </c>
       <c r="B15" s="20">
-        <v>131528.16105376347</v>
+        <v>131839.07791745692</v>
       </c>
       <c r="C15" s="20">
-        <v>-11844.050550887681</v>
+        <v>-11897.025238020928</v>
       </c>
       <c r="D15" s="21">
-        <v>-0.08261050323717994</v>
+        <v>-0.08276991637342526</v>
       </c>
       <c r="E15" s="20">
-        <v>8301.86989247312</v>
+        <v>8556.555075431035</v>
       </c>
       <c r="F15" s="20">
-        <v>21921.360175627244</v>
+        <v>21973.179652909486</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1454,19 +1454,19 @@
         <v>0.02</v>
       </c>
       <c r="B16" s="20">
-        <v>128464.73745263158</v>
+        <v>128762.63196983124</v>
       </c>
       <c r="C16" s="20">
-        <v>-14907.474152019568</v>
+        <v>-14973.471185646602</v>
       </c>
       <c r="D16" s="21">
-        <v>-0.1039774303902553</v>
+        <v>-0.10417334863635445</v>
       </c>
       <c r="E16" s="20">
-        <v>5626.449473684211</v>
+        <v>5870.117204641351</v>
       </c>
       <c r="F16" s="20">
-        <v>21410.789575438597</v>
+        <v>21460.43866163854</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1474,19 +1474,19 @@
         <v>0</v>
       </c>
       <c r="B17" s="23">
-        <v>125527.64059793815</v>
+        <v>125813.31188780992</v>
       </c>
       <c r="C17" s="23">
-        <v>-17844.571006713</v>
+        <v>-17922.791267667926</v>
       </c>
       <c r="D17" s="24">
-        <v>-0.1244632471452655</v>
+        <v>-0.12469234154957595</v>
       </c>
       <c r="E17" s="23">
-        <v>3061.3556701030934</v>
+        <v>3294.6891632231404</v>
       </c>
       <c r="F17" s="23">
-        <v>20921.273432989692</v>
+        <v>20968.885314634987</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1659,10 +1659,10 @@
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
       <c r="E34" s="36">
-        <v>3554.302325581395</v>
+        <v>3563.493006993007</v>
       </c>
       <c r="F34" s="36">
-        <v>3508.6206896551726</v>
+        <v>3517.600230414747</v>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2179,7 +2179,7 @@
       <c r="C29" s="47"/>
       <c r="D29" s="47"/>
       <c r="E29" s="53">
-        <v>690.5848837209303</v>
+        <v>712.9604778554778</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2192,7 +2192,7 @@
       <c r="C30" s="50"/>
       <c r="D30" s="50"/>
       <c r="E30" s="54">
-        <v>3452.9244186046512</v>
+        <v>3717.08520979021</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2205,7 +2205,7 @@
       <c r="C31" s="47"/>
       <c r="D31" s="47"/>
       <c r="E31" s="53">
-        <v>15192.867441860466</v>
+        <v>15228.28205128205</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2218,7 +2218,7 @@
       <c r="C32" s="50"/>
       <c r="D32" s="50"/>
       <c r="E32" s="54">
-        <v>18645.791860465117</v>
+        <v>18945.36726107226</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2231,7 +2231,7 @@
       <c r="C33" s="47"/>
       <c r="D33" s="47"/>
       <c r="E33" s="53">
-        <v>5255.234860465116</v>
+        <v>5297.175416550117</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2244,7 +2244,7 @@
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
       <c r="E34" s="57">
-        <v>143372.21160465115</v>
+        <v>143736.10315547785</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2257,7 +2257,7 @@
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
       <c r="E35" s="57">
-        <v>124726.41974418603</v>
+        <v>124790.73589440559</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="137">
   <si>
     <t>KALKULACJA NK6501</t>
   </si>
@@ -42,25 +42,37 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:28:47 · ceny netto w zł · szablon NK6501</t>
-  </si>
-  <si>
-    <t>Cena ofertowa · zysk 11%</t>
+    <t>Wygenerowano 27.10.2026, 14:33:08 · ceny netto w zł · szablon NK6501</t>
+  </si>
+  <si>
+    <t>Cena</t>
+  </si>
+  <si>
+    <t>Cena netto</t>
+  </si>
+  <si>
+    <t>Cena za MP</t>
+  </si>
+  <si>
+    <t>Rabat od oferty</t>
+  </si>
+  <si>
+    <t>Cena ofertowa · zysk 11% · 2000 kg · 5539 € / MP</t>
+  </si>
+  <si>
+    <t>–</t>
   </si>
   <si>
     <t>Można zejść do · zysk 10%</t>
   </si>
   <si>
-    <t>Próg opłacalności · zysk 0%</t>
-  </si>
-  <si>
-    <t>23 956 zł / MP · 5539 € / MP</t>
-  </si>
-  <si>
-    <t>rabat −1817 zł (−1,26%)</t>
-  </si>
-  <si>
-    <t>maks. rabat −17 923 zł (−12,47%)</t>
+    <t>−1817 zł (−1,26%)</t>
+  </si>
+  <si>
+    <t>Próg opłacalności · zysk 0% (maks. rabat)</t>
+  </si>
+  <si>
+    <t>−17 923 zł (−12,47%)</t>
   </si>
   <si>
     <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
@@ -69,21 +81,12 @@
     <t>Zysk</t>
   </si>
   <si>
-    <t>Cena netto</t>
-  </si>
-  <si>
-    <t>Rabat od oferty</t>
-  </si>
-  <si>
     <t>Rabat %</t>
   </si>
   <si>
     <t>Zysk z narzutem</t>
   </si>
   <si>
-    <t>Cena za MP</t>
-  </si>
-  <si>
     <t>Zielone: rabat bez zejścia poniżej zysku 10%. Żółte: poniżej zysku do porównania. Przy zysku 0% w cenie zostają koszty, KOB, GDW i podatek.</t>
   </si>
   <si>
@@ -126,7 +129,7 @@
     <t>KOB / GDW</t>
   </si>
   <si>
-    <t>0,52% / 2,69%</t>
+    <t>0,515% / 2,685%</t>
   </si>
   <si>
     <t>Opis wariantu</t>
@@ -168,28 +171,34 @@
     <t>Malowanie RAL</t>
   </si>
   <si>
-    <t>Konserwacja · wariant 1 · 6 MP</t>
-  </si>
-  <si>
-    <t>Konserwacja · wariant 2 · 6 MP</t>
-  </si>
-  <si>
-    <t>50 zł / MP / mies.</t>
-  </si>
-  <si>
-    <t>60 zł / MP / mies.</t>
-  </si>
-  <si>
-    <t>3600 zł rocznie</t>
-  </si>
-  <si>
-    <t>4320 zł rocznie</t>
-  </si>
-  <si>
-    <t>jeden przegląd (co pół roku): 1800 zł</t>
-  </si>
-  <si>
-    <t>jeden przegląd (co pół roku): 2160 zł</t>
+    <t>Konserwacja (6 MP)</t>
+  </si>
+  <si>
+    <t>Miesięcznie</t>
+  </si>
+  <si>
+    <t>Rocznie</t>
+  </si>
+  <si>
+    <t>Jeden przegląd (co pół roku)</t>
+  </si>
+  <si>
+    <t>35 zł / MP / mies.</t>
+  </si>
+  <si>
+    <t>40 zł / MP / mies.</t>
+  </si>
+  <si>
+    <t>45 zł / MP / mies.</t>
+  </si>
+  <si>
+    <t>50 zł / MP / mies.  · wariant 1</t>
+  </si>
+  <si>
+    <t>55 zł / MP / mies.</t>
+  </si>
+  <si>
+    <t>60 zł / MP / mies.  · wariant 2</t>
   </si>
   <si>
     <t>Pozostałe dane wejściowe</t>
@@ -225,7 +234,7 @@
     <t>4.325 / 3.86</t>
   </si>
   <si>
-    <t>Koszty krok po kroku · 2000 kg, zysk 11%</t>
+    <t>Koszty · 2000 kg · 11%</t>
   </si>
   <si>
     <t>Strona 1: obliczenia · strona 2: cennik szablonu NK6501</t>
@@ -357,13 +366,13 @@
     <t>KOB</t>
   </si>
   <si>
-    <t>0,52% ceny przed podatkiem (138 439 zł)</t>
+    <t>0,515% ceny przed podatkiem (138 439 zł)</t>
   </si>
   <si>
     <t>GDW</t>
   </si>
   <si>
-    <t>2,69% ceny przed podatkiem</t>
+    <t>2,685% ceny przed podatkiem</t>
   </si>
   <si>
     <t>Zysk 11%</t>
@@ -375,7 +384,7 @@
     <t>Zysk z narzutem (zysk + GDW)</t>
   </si>
   <si>
-    <t>zysk 11% + GDW 2,69%</t>
+    <t>zysk 11% + GDW 2,685%</t>
   </si>
   <si>
     <t>Podatek</t>
@@ -446,7 +455,7 @@
     <numFmt numFmtId="170" formatCode="&quot;+&quot;#,##0 &quot;zł&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -455,19 +464,19 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FFC4E4E7"/>
+      <color rgb="FF6A7780"/>
       <sz val="8"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="15"/>
+      <color rgb="FF0E171C"/>
+      <sz val="16"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0E171C"/>
       <sz val="13"/>
       <name val="Arial"/>
     </font>
@@ -479,13 +488,18 @@
     <font>
       <b/>
       <color rgb="FF0A6B74"/>
-      <sz val="16"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF0E171C"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="16"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -497,23 +511,12 @@
     <font>
       <b/>
       <color rgb="FF0A6B74"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF13794A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -540,22 +543,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF0E171C"/>
-      <sz val="9.5"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
-      <sz val="9.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF6A7780"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -572,22 +559,12 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0A6B74"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3F8F8"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -620,49 +597,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D9DD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D9DD"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF0A6B74"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D9DD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D9DD"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D9DD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D9DD"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD3D9DD"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -692,8 +632,8 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color rgb="FF0A6B74"/>
+      <top style="thin">
+        <color rgb="FFD3D9DD"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -711,188 +651,180 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1234,13 +1166,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="17" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1277,533 +1211,612 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="F5" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9">
         <v>143736.10315547785</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7">
+      <c r="E6" s="9">
+        <v>23956.017192579642</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9">
         <v>141919.0459762673</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8">
+      <c r="E7" s="9">
+        <v>23653.174329377885</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9">
         <v>125813.31188780992</v>
       </c>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="E8" s="9">
+        <v>20968.885314634987</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="11" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+      <c r="E11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
         <v>0.11</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B12" s="15">
         <v>143736.10315547785</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C12" s="15">
         <v>0</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D12" s="16">
         <v>0</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E12" s="15">
         <v>18945.36726107226</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F12" s="15">
         <v>23956.017192579642</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
         <v>0.1</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B13" s="18">
         <v>141919.0459762673</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C13" s="18">
         <v>-1817.057179210533</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D13" s="19">
         <v>-0.012641619880601892</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E13" s="18">
         <v>17358.66256912443</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F13" s="18">
         <v>23653.174329377885</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="20">
         <v>0.08</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B14" s="21">
         <v>138407.70575157658</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C14" s="21">
         <v>-5328.397403901268</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D14" s="22">
         <v>-0.03707069613636037</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E14" s="21">
         <v>14292.462961711713</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F14" s="21">
         <v>23067.950958596095</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="20">
         <v>0.06</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B15" s="21">
         <v>135051.05011828194</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C15" s="21">
         <v>-8685.053037195903</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D15" s="22">
         <v>-0.06042360163195305</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E15" s="21">
         <v>11361.338226872247</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F15" s="21">
         <v>22508.50835304699</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="20">
         <v>0.04</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B16" s="21">
         <v>131839.07791745692</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C16" s="21">
         <v>-11897.025238020928</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D16" s="22">
         <v>-0.08276991637342526</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E16" s="21">
         <v>8556.555075431035</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F16" s="21">
         <v>21973.179652909486</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="20">
         <v>0.02</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B17" s="21">
         <v>128762.63196983124</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C17" s="21">
         <v>-14973.471185646602</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D17" s="22">
         <v>-0.10417334863635445</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E17" s="21">
         <v>5870.117204641351</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F17" s="21">
         <v>21460.43866163854</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="22">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="23">
         <v>0</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="24">
         <v>125813.31188780992</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C18" s="24">
         <v>-17922.791267667926</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D18" s="25">
         <v>-0.12469234154957595</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E18" s="24">
         <v>3294.6891632231404</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F18" s="24">
         <v>20968.885314634987</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+    <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26" t="s">
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="27" t="s">
         <v>21</v>
-      </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-    </row>
-    <row r="22" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
-        <v>22</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="27"/>
       <c r="D22" s="27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
     </row>
-    <row r="23" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-    </row>
-    <row r="24" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27" t="s">
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+    </row>
+    <row r="25" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29" t="s">
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-    </row>
-    <row r="26" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27" t="s">
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+    </row>
+    <row r="27" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29" t="s">
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="32" t="s">
+      <c r="B30" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="33" t="s">
         <v>36</v>
-      </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" s="32"/>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="33" t="s">
-        <v>38</v>
       </c>
       <c r="B31" s="33"/>
       <c r="C31" s="33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D31" s="33"/>
       <c r="E31" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="33"/>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="F31" s="33"/>
-    </row>
-    <row r="33" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="D32" s="34"/>
+      <c r="E32" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="F32" s="34"/>
+    </row>
+    <row r="34" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12" t="s">
+      <c r="B34" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="13" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="34" t="s">
+      <c r="F34" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="36">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="37">
         <v>3563.493006993007</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F35" s="37">
         <v>3517.600230414747</v>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37" t="s">
+    <row r="37" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="38" t="s">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38" t="s">
+      <c r="E37" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-    </row>
-    <row r="38" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="39" t="s">
+      <c r="F37" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39" t="s">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="40" t="s">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="38">
+        <v>210</v>
+      </c>
+      <c r="E38" s="38">
+        <v>2520</v>
+      </c>
+      <c r="F38" s="38">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="40"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40" t="s">
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="38">
+        <v>240</v>
+      </c>
+      <c r="E39" s="38">
+        <v>2880</v>
+      </c>
+      <c r="F39" s="38">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-    </row>
-    <row r="41" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="38">
+        <v>270</v>
+      </c>
+      <c r="E40" s="38">
+        <v>3240</v>
+      </c>
+      <c r="F40" s="38">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="9">
+        <v>300</v>
+      </c>
+      <c r="E41" s="9">
+        <v>3600</v>
+      </c>
+      <c r="F41" s="9">
+        <v>1800</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="41" t="s">
+      <c r="A42" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="42" t="s">
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="38">
+        <v>330</v>
+      </c>
+      <c r="E42" s="38">
+        <v>3960</v>
+      </c>
+      <c r="F42" s="38">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="41" t="s">
+      <c r="B43" s="39"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="9">
+        <v>360</v>
+      </c>
+      <c r="E43" s="9">
+        <v>4320</v>
+      </c>
+      <c r="F43" s="9">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="42" t="s">
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="41" t="s">
+      <c r="B46" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="41" t="s">
+      <c r="B47" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B45" s="42" t="s">
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="41" t="s">
+      <c r="B48" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B46" s="42" t="s">
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
+      <c r="B49" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="48">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="A23:C23"/>
@@ -1816,29 +1829,30 @@
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="A37:C37"/>
-    <mergeCell ref="D37:F37"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:F38"/>
     <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
@@ -1857,500 +1871,500 @@
     <col min="2" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
+    <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="A2" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="A4" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
+      <c r="A5" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
+      <c r="A6" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
+      <c r="A7" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="46">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="46">
+        <v>15.98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="49">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="50">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="49">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="51">
+        <v>82900</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="52">
+        <v>3729</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="51">
+        <v>6760</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="52">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="51">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="52">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="51">
+        <v>5242.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="52">
+        <v>10875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="51">
+        <v>2024.1000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="55">
+        <v>118780.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="51">
+        <v>712.9604778554778</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="52">
+        <v>3717.08520979021</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="51">
+        <v>15228.28205128205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="52">
+        <v>18945.36726107226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="51">
+        <v>5297.175416550117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="55">
+        <v>143736.10315547785</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="55">
+        <v>124790.73589440559</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="42"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+    </row>
+    <row r="39" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39" s="56"/>
+      <c r="E39" s="57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="59">
+        <v>130</v>
+      </c>
+      <c r="C40" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="45" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="46" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="48">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="51">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="48">
-        <v>15.98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="51">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="52">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="51">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="53">
-        <v>82900</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="54">
-        <v>3729</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="B21" s="47" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="53">
-        <v>6760</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="54">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="53">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="B24" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="54">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="53">
-        <v>5242.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="54">
-        <v>10875</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="53">
-        <v>2024.1000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="B28" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="57">
-        <v>118780.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="46" t="s">
-        <v>108</v>
-      </c>
-      <c r="B29" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="53">
-        <v>712.9604778554778</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="B30" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="54">
-        <v>3717.08520979021</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="53">
-        <v>15228.28205128205</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="54">
-        <v>18945.36726107226</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="53">
-        <v>5297.175416550117</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="55" t="s">
-        <v>118</v>
-      </c>
-      <c r="B34" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="57">
-        <v>143736.10315547785</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="B35" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="57">
-        <v>124790.73589440559</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="B36" s="43"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-    </row>
-    <row r="39" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="59" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="D39" s="58"/>
-      <c r="E39" s="59" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="B40" s="61">
+      <c r="D40" s="58"/>
+      <c r="E40" s="60" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="C40" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="60"/>
-      <c r="E40" s="62" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="41" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="B41" s="61">
+      <c r="B41" s="59">
         <v>45</v>
       </c>
-      <c r="C41" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41" s="60"/>
-      <c r="E41" s="62" t="s">
-        <v>128</v>
+      <c r="C41" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41" s="58"/>
+      <c r="E41" s="60" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="B42" s="59" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" s="60" t="s">
-        <v>130</v>
-      </c>
-      <c r="D42" s="60"/>
-      <c r="E42" s="62" t="s">
-        <v>131</v>
+      <c r="A42" s="56" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" s="58"/>
+      <c r="E42" s="60" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="B43" s="62" t="s">
-        <v>133</v>
+      <c r="A43" s="58" t="s">
+        <v>135</v>
+      </c>
+      <c r="B43" s="60" t="s">
+        <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D43"/>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -39,10 +39,10 @@
     <t>ul. Ogrodowa 8, Warszawa</t>
   </si>
   <si>
-    <t>21.10.2026</t>
-  </si>
-  <si>
-    <t>Wygenerowano 27.10.2026, 14:33:08 · ceny netto w zł · szablon NK6501</t>
+    <t>21.10.2026, 14:43</t>
+  </si>
+  <si>
+    <t>Wygenerowano 27.10.2026, 14:43:39 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -39,10 +39,10 @@
     <t>ul. Ogrodowa 8, Warszawa</t>
   </si>
   <si>
-    <t>21.10.2026, 14:43</t>
-  </si>
-  <si>
-    <t>Wygenerowano 27.10.2026, 14:43:39 · ceny netto w zł · szablon NK6501</t>
+    <t>21.10.2026, 17:30</t>
+  </si>
+  <si>
+    <t>Wygenerowano 27.10.2026, 17:30:54 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena</t>
@@ -597,7 +597,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -647,6 +647,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD3D9DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -818,13 +827,13 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -39,10 +39,10 @@
     <t>ul. Ogrodowa 8, Warszawa</t>
   </si>
   <si>
-    <t>21.10.2026, 17:30</t>
-  </si>
-  <si>
-    <t>Wygenerowano 27.10.2026, 17:30:54 · ceny netto w zł · szablon NK6501</t>
+    <t>21.10.2026, 10:10</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 10:10:16 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -4,29 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Podsumowanie" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Obliczenia i cennik" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Kalkulacja" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="B40" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B41" authorId="0">
-      <text/>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="137">
   <si>
@@ -39,10 +22,10 @@
     <t>ul. Ogrodowa 8, Warszawa</t>
   </si>
   <si>
-    <t>21.10.2026, 10:10</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 10:10:16 · ceny netto w zł · szablon NK6501</t>
+    <t>21.10.2026, 10:28</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 10:28:00 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena</t>
@@ -201,6 +184,183 @@
     <t>60 zł / MP / mies.  · wariant 2</t>
   </si>
   <si>
+    <t>Koszty · 2000 kg · 11%</t>
+  </si>
+  <si>
+    <t>Skąd się biorą kwoty (wariant 2000 kg) · ceny netto w zł</t>
+  </si>
+  <si>
+    <t>Materiały i urządzenia</t>
+  </si>
+  <si>
+    <t>Palety NK6501: 6 × 9500 zł</t>
+  </si>
+  <si>
+    <t>57 000 zł</t>
+  </si>
+  <si>
+    <t>Silnik, przekładnia i reszta</t>
+  </si>
+  <si>
+    <t>6000 zł</t>
+  </si>
+  <si>
+    <t>Sterowanie palet (Mufas)</t>
+  </si>
+  <si>
+    <t>19 900 zł</t>
+  </si>
+  <si>
+    <t>Malowanie RAL (opcja, poza ceną)</t>
+  </si>
+  <si>
+    <t>3000 zł</t>
+  </si>
+  <si>
+    <t>Suma 2000 kg</t>
+  </si>
+  <si>
+    <t>82 900 zł</t>
+  </si>
+  <si>
+    <t>Montaż, narzuty i cena</t>
+  </si>
+  <si>
+    <t>Pozycja</t>
+  </si>
+  <si>
+    <t>Skąd ta kwota</t>
+  </si>
+  <si>
+    <t>Kwota</t>
+  </si>
+  <si>
+    <t>Osobodni montażu</t>
+  </si>
+  <si>
+    <t>z cennika osobodni na urządzenie + utrudnienia</t>
+  </si>
+  <si>
+    <t>Tygodnie / dni montażu</t>
+  </si>
+  <si>
+    <t>tygodniowe wyjazdy ekipy</t>
+  </si>
+  <si>
+    <t>Osobodni podróży i rozładunku</t>
+  </si>
+  <si>
+    <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
+  </si>
+  <si>
+    <t>Dni pracy ekipy</t>
+  </si>
+  <si>
+    <t>(osd montażu + podróży) ÷ 4 os.</t>
+  </si>
+  <si>
+    <t>Kilometry auta</t>
+  </si>
+  <si>
+    <t>dojazdy na montaż, pomiary i odbiory w obie strony</t>
+  </si>
+  <si>
+    <t>Noclegi (osobonoce)</t>
+  </si>
+  <si>
+    <t>(dni pracy + 1) × 4 os.</t>
+  </si>
+  <si>
+    <t>cena urządzeń i pozycji kosztowych (patrz wyżej)</t>
+  </si>
+  <si>
+    <t>Paliwo</t>
+  </si>
+  <si>
+    <t>3300 km × 113 zł/100 km (12 l × 9,4 zł)</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>52 noclegów × 130 zł/doba</t>
+  </si>
+  <si>
+    <t>Rozładunek, sprzęt</t>
+  </si>
+  <si>
+    <t>3000 zł jednorazowo</t>
+  </si>
+  <si>
+    <t>Rozładunek, ludzie</t>
+  </si>
+  <si>
+    <t>0,5 dni × 4 os. × 375 zł</t>
+  </si>
+  <si>
+    <t>Dojazdy, ludzie</t>
+  </si>
+  <si>
+    <t>13,98 osd podróży × 375 zł</t>
+  </si>
+  <si>
+    <t>29 osd × 375 zł (średnia stawka)</t>
+  </si>
+  <si>
+    <t>Diety</t>
+  </si>
+  <si>
+    <t>44,98 osd × 45 zł</t>
+  </si>
+  <si>
+    <t>Suma przed narzutami</t>
+  </si>
+  <si>
+    <t>suma kosztów powyżej</t>
+  </si>
+  <si>
+    <t>KOB</t>
+  </si>
+  <si>
+    <t>0,515% ceny przed podatkiem (138 439 zł)</t>
+  </si>
+  <si>
+    <t>GDW</t>
+  </si>
+  <si>
+    <t>2,685% ceny przed podatkiem</t>
+  </si>
+  <si>
+    <t>Zysk 11%</t>
+  </si>
+  <si>
+    <t>11% ceny przed podatkiem</t>
+  </si>
+  <si>
+    <t>Zysk z narzutem (zysk + GDW)</t>
+  </si>
+  <si>
+    <t>zysk 11% + GDW 2,685%</t>
+  </si>
+  <si>
+    <t>Podatek</t>
+  </si>
+  <si>
+    <t>14% od robocizny (18 892 zł) i zysku z narzutem</t>
+  </si>
+  <si>
+    <t>Cena kontraktu, zysk 11%</t>
+  </si>
+  <si>
+    <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>
+  </si>
+  <si>
+    <t>Koszt rzeczywisty</t>
+  </si>
+  <si>
+    <t>cena − zysk z narzutem</t>
+  </si>
+  <si>
     <t>Pozostałe dane wejściowe</t>
   </si>
   <si>
@@ -210,12 +370,6 @@
     <t>300 / 350 km</t>
   </si>
   <si>
-    <t>Sterowanie palet (Mufas)</t>
-  </si>
-  <si>
-    <t>19 900 zł</t>
-  </si>
-  <si>
     <t>Utrudnienia</t>
   </si>
   <si>
@@ -234,181 +388,10 @@
     <t>4.325 / 3.86</t>
   </si>
   <si>
-    <t>Koszty · 2000 kg · 11%</t>
-  </si>
-  <si>
-    <t>Strona 1: obliczenia · strona 2: cennik szablonu NK6501</t>
-  </si>
-  <si>
-    <t>Materiały i urządzenia</t>
-  </si>
-  <si>
-    <t>Palety NK6501: 6 × 9500 zł</t>
-  </si>
-  <si>
-    <t>57 000 zł</t>
-  </si>
-  <si>
-    <t>Silnik, przekładnia i reszta</t>
-  </si>
-  <si>
-    <t>6000 zł</t>
-  </si>
-  <si>
-    <t>Malowanie RAL (opcja, poza ceną)</t>
-  </si>
-  <si>
-    <t>3000 zł</t>
-  </si>
-  <si>
-    <t>Suma 2000 kg</t>
-  </si>
-  <si>
-    <t>82 900 zł</t>
-  </si>
-  <si>
-    <t>Montaż, narzuty i cena</t>
-  </si>
-  <si>
-    <t>Pozycja</t>
-  </si>
-  <si>
-    <t>Skąd ta kwota</t>
-  </si>
-  <si>
-    <t>Kwota</t>
-  </si>
-  <si>
-    <t>Osobodni montażu</t>
-  </si>
-  <si>
-    <t>z cennika osobodni na urządzenie + utrudnienia</t>
-  </si>
-  <si>
-    <t>Tygodnie / dni montażu</t>
-  </si>
-  <si>
-    <t>tygodniowe wyjazdy ekipy</t>
-  </si>
-  <si>
-    <t>Osobodni podróży i rozładunku</t>
-  </si>
-  <si>
-    <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
-  </si>
-  <si>
-    <t>Dni pracy ekipy</t>
-  </si>
-  <si>
-    <t>(osd montażu + podróży) ÷ 4 os.</t>
-  </si>
-  <si>
-    <t>Kilometry auta</t>
-  </si>
-  <si>
-    <t>dojazdy na montaż, pomiary i odbiory w obie strony</t>
-  </si>
-  <si>
-    <t>Noclegi (osobonoce)</t>
-  </si>
-  <si>
-    <t>(dni pracy + 1) × 4 os.</t>
-  </si>
-  <si>
-    <t>cena urządzeń i pozycji kosztowych (patrz wyżej)</t>
-  </si>
-  <si>
-    <t>Paliwo</t>
-  </si>
-  <si>
-    <t>3300 km × 113 zł/100 km (12 l × 9,4 zł)</t>
-  </si>
-  <si>
-    <t>Hotel</t>
-  </si>
-  <si>
-    <t>52 noclegów × 130 zł/doba</t>
-  </si>
-  <si>
-    <t>Rozładunek, sprzęt</t>
-  </si>
-  <si>
-    <t>3000 zł jednorazowo</t>
-  </si>
-  <si>
-    <t>Rozładunek, ludzie</t>
-  </si>
-  <si>
-    <t>0,5 dni × 4 os. × 375 zł</t>
-  </si>
-  <si>
-    <t>Dojazdy, ludzie</t>
-  </si>
-  <si>
-    <t>13,98 osd podróży × 375 zł</t>
-  </si>
-  <si>
-    <t>29 osd × 375 zł (średnia stawka)</t>
-  </si>
-  <si>
-    <t>Diety</t>
-  </si>
-  <si>
-    <t>44,98 osd × 45 zł</t>
-  </si>
-  <si>
-    <t>Suma przed narzutami</t>
-  </si>
-  <si>
-    <t>suma kosztów powyżej</t>
-  </si>
-  <si>
-    <t>KOB</t>
-  </si>
-  <si>
-    <t>0,515% ceny przed podatkiem (138 439 zł)</t>
-  </si>
-  <si>
-    <t>GDW</t>
-  </si>
-  <si>
-    <t>2,685% ceny przed podatkiem</t>
-  </si>
-  <si>
-    <t>Zysk 11%</t>
-  </si>
-  <si>
-    <t>11% ceny przed podatkiem</t>
-  </si>
-  <si>
-    <t>Zysk z narzutem (zysk + GDW)</t>
-  </si>
-  <si>
-    <t>zysk 11% + GDW 2,685%</t>
-  </si>
-  <si>
-    <t>Podatek</t>
-  </si>
-  <si>
-    <t>14% od robocizny (18 892 zł) i zysku z narzutem</t>
-  </si>
-  <si>
-    <t>Cena kontraktu, zysk 11%</t>
-  </si>
-  <si>
-    <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>
-  </si>
-  <si>
-    <t>Koszt rzeczywisty</t>
-  </si>
-  <si>
-    <t>cena − zysk z narzutem</t>
-  </si>
-  <si>
     <t>Cennik szablonu NK6501</t>
   </si>
   <si>
-    <t>Pomarańczowe = zmienione względem domyślnego NK38</t>
+    <t>Pomarańczowe = zmienione względem domyślnego NK6501</t>
   </si>
   <si>
     <t>Pozycje kosztowe</t>
@@ -660,7 +643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -777,18 +760,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -827,11 +810,17 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="3"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1175,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1742,78 +1731,614 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
+    <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="40" t="s">
+      <c r="A46" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="B46" s="41" t="s">
-        <v>59</v>
-      </c>
+      <c r="B46" s="41"/>
       <c r="C46" s="41"/>
       <c r="D46" s="41"/>
       <c r="E46" s="41"/>
       <c r="F46" s="41"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="40" t="s">
+    <row r="48" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="41" t="s">
+      <c r="B49" s="42"/>
+      <c r="C49" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="40" t="s">
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="B48" s="41" t="s">
+      <c r="B50" s="42"/>
+      <c r="C50" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="40" t="s">
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="41" t="s">
+      <c r="B51" s="42"/>
+      <c r="C51" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="40" t="s">
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="41" t="s">
+      <c r="B52" s="42"/>
+      <c r="C52" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="42"/>
+      <c r="C53" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
+    </row>
+    <row r="55" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+    </row>
+    <row r="56" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="44"/>
+      <c r="C57" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57" s="45"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="46">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58" s="47"/>
+      <c r="C58" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59" s="44"/>
+      <c r="C59" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D59" s="45"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="46">
+        <v>15.98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="B60" s="47"/>
+      <c r="C60" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" s="48"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="49">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="44"/>
+      <c r="C61" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="45"/>
+      <c r="E61" s="45"/>
+      <c r="F61" s="50">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" s="47"/>
+      <c r="C62" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="49">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" s="44"/>
+      <c r="C63" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D63" s="45"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="51">
+        <v>82900</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B64" s="47"/>
+      <c r="C64" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="D64" s="48"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="52">
+        <v>3729</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" s="44"/>
+      <c r="C65" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="51">
+        <v>6760</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="47"/>
+      <c r="C66" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="52">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B67" s="44"/>
+      <c r="C67" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="D67" s="45"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="51">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" s="47"/>
+      <c r="C68" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="D68" s="48"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="52">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="B69" s="44"/>
+      <c r="C69" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="D69" s="45"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="51">
+        <v>5242.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" s="47"/>
+      <c r="C70" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="52">
+        <v>10875</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B71" s="44"/>
+      <c r="C71" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="D71" s="45"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="51">
+        <v>2024.1000000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B72" s="53"/>
+      <c r="C72" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="D72" s="54"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="55">
+        <v>118780.6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" s="44"/>
+      <c r="C73" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="D73" s="45"/>
+      <c r="E73" s="45"/>
+      <c r="F73" s="51">
+        <v>712.9604778554778</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B74" s="47"/>
+      <c r="C74" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="52">
+        <v>3717.08520979021</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" s="44"/>
+      <c r="C75" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="51">
+        <v>15228.28205128205</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="B76" s="47"/>
+      <c r="C76" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="52">
+        <v>18945.36726107226</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" s="44"/>
+      <c r="C77" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="D77" s="45"/>
+      <c r="E77" s="45"/>
+      <c r="F77" s="51">
+        <v>5297.175416550117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" s="53"/>
+      <c r="C78" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D78" s="54"/>
+      <c r="E78" s="54"/>
+      <c r="F78" s="55">
+        <v>143736.10315547785</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B79" s="53"/>
+      <c r="C79" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="D79" s="54"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="55">
+        <v>124790.73589440559</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="B82" s="42"/>
+      <c r="C82" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D82" s="43"/>
+      <c r="E82" s="43"/>
+      <c r="F82" s="43"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B83" s="42"/>
+      <c r="C83" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="D83" s="43"/>
+      <c r="E83" s="43"/>
+      <c r="F83" s="43"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="B84" s="42"/>
+      <c r="C84" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="D84" s="43"/>
+      <c r="E84" s="43"/>
+      <c r="F84" s="43"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="B85" s="42"/>
+      <c r="C85" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="D85" s="43"/>
+      <c r="E85" s="43"/>
+      <c r="F85" s="43"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="B86" s="42"/>
+      <c r="C86" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" s="43"/>
+      <c r="E86" s="43"/>
+      <c r="F86" s="43"/>
+    </row>
+    <row r="88" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B88" s="40"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="B89" s="41"/>
+      <c r="C89" s="41"/>
+      <c r="D89" s="41"/>
+      <c r="E89" s="41"/>
+      <c r="F89" s="41"/>
+    </row>
+    <row r="91" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="B91" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="D91" s="58"/>
+      <c r="E91" s="58"/>
+      <c r="F91" s="57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="B92" s="60">
+        <v>130</v>
+      </c>
+      <c r="C92" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="D92" s="61"/>
+      <c r="E92" s="61"/>
+      <c r="F92" s="62" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="93" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B93" s="60">
+        <v>45</v>
+      </c>
+      <c r="C93" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="D93" s="61"/>
+      <c r="E93" s="61"/>
+      <c r="F93" s="62" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="94" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="56" t="s">
+        <v>132</v>
+      </c>
+      <c r="B94" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" s="61" t="s">
+        <v>133</v>
+      </c>
+      <c r="D94" s="61"/>
+      <c r="E94" s="61"/>
+      <c r="F94" s="62" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="95" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="B95" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C95" t="s">
+        <v>31</v>
+      </c>
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="122">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -1857,576 +2382,94 @@
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A45:F45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:F82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:F83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:F84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C85:F85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:F86"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C95:E95"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="78" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8ul. Ogrodowa 8, Warszawa&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
   </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="5" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="46">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="46">
-        <v>15.98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="49">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="50">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="49">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="51">
-        <v>82900</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="52">
-        <v>3729</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="51">
-        <v>6760</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="52">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="51">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="52">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="B25" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="51">
-        <v>5242.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="52">
-        <v>10875</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="B27" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="51">
-        <v>2024.1000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="B28" s="54" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="55">
-        <v>118780.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="44" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="51">
-        <v>712.9604778554778</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="52">
-        <v>3717.08520979021</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="51">
-        <v>15228.28205128205</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="48" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="52">
-        <v>18945.36726107226</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="B33" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="51">
-        <v>5297.175416550117</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="B34" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="55">
-        <v>143736.10315547785</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="B35" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="C35" s="54"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="55">
-        <v>124790.73589440559</v>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="B36" s="42"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="B37" s="43"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-    </row>
-    <row r="39" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="56" t="s">
-        <v>127</v>
-      </c>
-      <c r="D39" s="56"/>
-      <c r="E39" s="57" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="B40" s="59">
-        <v>130</v>
-      </c>
-      <c r="C40" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="D40" s="58"/>
-      <c r="E40" s="60" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="41" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="58" t="s">
-        <v>130</v>
-      </c>
-      <c r="B41" s="59">
-        <v>45</v>
-      </c>
-      <c r="C41" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="D41" s="58"/>
-      <c r="E41" s="60" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="B42" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="58" t="s">
-        <v>133</v>
-      </c>
-      <c r="D42" s="58"/>
-      <c r="E42" s="60" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="58" t="s">
-        <v>135</v>
-      </c>
-      <c r="B43" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="C43" t="s">
-        <v>31</v>
-      </c>
-      <c r="D43"/>
-      <c r="E43" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-  </mergeCells>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="82" fitToWidth="1" fitToHeight="1"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8ul. Ogrodowa 8, Warszawa&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="35" max="16838" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="44" max="16838" man="1"/>
+    <brk id="87" max="16838" man="1"/>
   </rowBreaks>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -22,10 +22,10 @@
     <t>ul. Ogrodowa 8, Warszawa</t>
   </si>
   <si>
-    <t>21.10.2026, 10:28</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 10:28:00 · ceny netto w zł · szablon NK6501</t>
+    <t>21.10.2026, 11:44</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 11:44:46 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena</t>
@@ -643,7 +643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -817,13 +817,16 @@
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2325,7 +2328,7 @@
       <c r="A95" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B95" s="62" t="s">
+      <c r="B95" s="63" t="s">
         <v>136</v>
       </c>
       <c r="C95" t="s">

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -22,10 +22,10 @@
     <t>ul. Ogrodowa 8, Warszawa</t>
   </si>
   <si>
-    <t>21.10.2026, 11:44</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 11:44:46 · ceny netto w zł · szablon NK6501</t>
+    <t>21.10.2026, 12:42</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 12:42:33 · ceny netto w zł · szablon NK6501</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Ogrodowa_8_Warszawa_NK6501.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="138">
   <si>
     <t>KALKULACJA NK6501</t>
   </si>
@@ -22,10 +22,10 @@
     <t>ul. Ogrodowa 8, Warszawa</t>
   </si>
   <si>
-    <t>21.10.2026, 12:42</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 12:42:33 · ceny netto w zł · szablon NK6501</t>
+    <t>21.10.2026, 12:45</t>
+  </si>
+  <si>
+    <t>Ceny netto · wygenerowano 30.10.2026</t>
   </si>
   <si>
     <t>Cena</t>
@@ -40,7 +40,10 @@
     <t>Rabat od oferty</t>
   </si>
   <si>
-    <t>Cena ofertowa · zysk 11% · 2000 kg · 5539 € / MP</t>
+    <t>Cena ofertowa · zysk 11% · 2000 kg</t>
+  </si>
+  <si>
+    <t>23 956 zł · 5539 €</t>
   </si>
   <si>
     <t>–</t>
@@ -52,13 +55,13 @@
     <t>−1817 zł (−1,26%)</t>
   </si>
   <si>
-    <t>Próg opłacalności · zysk 0% (maks. rabat)</t>
+    <t>Próg opłacalności · zysk 0% · maks. rabat</t>
   </si>
   <si>
     <t>−17 923 zł (−12,47%)</t>
   </si>
   <si>
-    <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
+    <t>Pole do negocjacji (2000 kg)</t>
   </si>
   <si>
     <t>Zysk</t>
@@ -438,7 +441,7 @@
     <numFmt numFmtId="170" formatCode="&quot;+&quot;#,##0 &quot;zł&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -448,98 +451,104 @@
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="8"/>
-      <name val="Arial"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="16"/>
-      <name val="Arial"/>
+      <sz val="17.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="13"/>
-      <name val="Arial"/>
+      <sz val="14.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="9"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF0E171C"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0E171C"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF13794A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FFB42318"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF6A7780"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0A6B74"/>
       <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF13794A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFB42318"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF6A7780"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="8"/>
-      <name val="Arial"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="11"/>
-      <name val="Arial"/>
+      <sz val="11.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF6A7780"/>
-      <sz val="9"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF0E171C"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -580,7 +589,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -613,12 +622,40 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
       <top style="thin">
         <color rgb="FFD3D9DD"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD3D9DD"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -643,7 +680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -722,21 +759,24 @@
       <alignment wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -766,7 +806,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -802,30 +842,30 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="3"/>
     </xf>
   </cellXfs>
@@ -1167,7 +1207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1237,16 +1277,16 @@
       <c r="D6" s="9">
         <v>143736.10315547785</v>
       </c>
-      <c r="E6" s="9">
-        <v>23956.017192579642</v>
+      <c r="E6" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1257,12 +1297,12 @@
         <v>23653.174329377885</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1273,12 +1313,12 @@
         <v>20968.885314634987</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1288,7 +1328,7 @@
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>6</v>
@@ -1297,10 +1337,10 @@
         <v>8</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>7</v>
@@ -1448,7 +1488,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="26"/>
@@ -1458,7 +1498,7 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1468,95 +1508,93 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="27"/>
       <c r="D22" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
     </row>
     <row r="23" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
       <c r="D23" s="28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" s="29"/>
       <c r="C24" s="29"/>
       <c r="D24" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E24" s="30"/>
       <c r="F24" s="30"/>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" s="28"/>
       <c r="C25" s="28"/>
       <c r="D25" s="28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E25" s="28"/>
       <c r="F25" s="28"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
       <c r="D26" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E26" s="30"/>
       <c r="F26" s="30"/>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
       <c r="D27" s="28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E27" s="28"/>
       <c r="F27" s="28"/>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
+      <c r="A28" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="32" t="s">
+      <c r="A30" s="32" t="s">
         <v>35</v>
       </c>
+      <c r="B30" s="32"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="E30" s="32"/>
@@ -1567,91 +1605,85 @@
         <v>36</v>
       </c>
       <c r="B31" s="33"/>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="34" t="s">
         <v>37</v>
-      </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="33"/>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="34" t="s">
-        <v>39</v>
       </c>
       <c r="B32" s="34"/>
       <c r="C32" s="34" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D32" s="34"/>
       <c r="E32" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="34"/>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="34"/>
-    </row>
-    <row r="34" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
+      <c r="D33" s="35"/>
+      <c r="E33" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="F33" s="35"/>
+    </row>
+    <row r="35" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="13" t="s">
+      <c r="B35" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="35" t="s">
+      <c r="F35" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B35" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="37">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="38">
         <v>3563.493006993007</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F36" s="38">
         <v>3517.600230414747</v>
       </c>
     </row>
-    <row r="37" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="13" t="s">
+    <row r="38" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="E38" s="13" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+      <c r="F38" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="38">
-        <v>210</v>
-      </c>
-      <c r="E38" s="38">
-        <v>2520</v>
-      </c>
-      <c r="F38" s="38">
-        <v>1260</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1660,14 +1692,14 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="38">
-        <v>240</v>
-      </c>
-      <c r="E39" s="38">
-        <v>2880</v>
-      </c>
-      <c r="F39" s="38">
-        <v>1440</v>
+      <c r="D39" s="39">
+        <v>210</v>
+      </c>
+      <c r="E39" s="39">
+        <v>2520</v>
+      </c>
+      <c r="F39" s="39">
+        <v>1260</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1676,75 +1708,81 @@
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
-      <c r="D40" s="38">
+      <c r="D40" s="39">
+        <v>240</v>
+      </c>
+      <c r="E40" s="39">
+        <v>2880</v>
+      </c>
+      <c r="F40" s="39">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="39">
         <v>270</v>
       </c>
-      <c r="E40" s="38">
+      <c r="E41" s="39">
         <v>3240</v>
       </c>
-      <c r="F40" s="38">
+      <c r="F41" s="39">
         <v>1620</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" s="39"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="9">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="40"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="9">
         <v>300</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E42" s="9">
         <v>3600</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F42" s="9">
         <v>1800</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="38">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="39">
         <v>330</v>
       </c>
-      <c r="E42" s="38">
+      <c r="E43" s="39">
         <v>3960</v>
       </c>
-      <c r="F42" s="38">
+      <c r="F43" s="39">
         <v>1980</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" s="39"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="9">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="40"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="9">
         <v>360</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E44" s="9">
         <v>4320</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F44" s="9">
         <v>2160</v>
       </c>
     </row>
-    <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45" s="40"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="40"/>
-      <c r="E45" s="40"/>
-      <c r="F45" s="40"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="41" t="s">
         <v>58</v>
       </c>
@@ -1754,503 +1792,503 @@
       <c r="E46" s="41"/>
       <c r="F46" s="41"/>
     </row>
-    <row r="48" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="42" t="s">
+      <c r="B47" s="42"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+    </row>
+    <row r="49" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="42"/>
-      <c r="C49" s="43" t="s">
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="42" t="s">
+      <c r="B50" s="43"/>
+      <c r="C50" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="B50" s="42"/>
-      <c r="C50" s="43" t="s">
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="42" t="s">
+      <c r="B51" s="43"/>
+      <c r="C51" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="B51" s="42"/>
-      <c r="C51" s="43" t="s">
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="42" t="s">
+      <c r="B52" s="43"/>
+      <c r="C52" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="B52" s="42"/>
-      <c r="C52" s="43" t="s">
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="42" t="s">
+      <c r="B53" s="43"/>
+      <c r="C53" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="B53" s="42"/>
-      <c r="C53" s="43" t="s">
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="D53" s="43"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-    </row>
-    <row r="55" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+      <c r="B54" s="43"/>
+      <c r="C54" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-    </row>
-    <row r="56" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+    </row>
+    <row r="56" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6" t="s">
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+    </row>
+    <row r="57" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="7" t="s">
+      <c r="B57" s="6"/>
+      <c r="C57" s="6" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="44" t="s">
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B57" s="44"/>
-      <c r="C57" s="45" t="s">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="D57" s="45"/>
-      <c r="E57" s="45"/>
-      <c r="F57" s="46">
+      <c r="B58" s="45"/>
+      <c r="C58" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="47">
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="B58" s="47"/>
-      <c r="C58" s="48" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="49">
+      <c r="B59" s="48"/>
+      <c r="C59" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="50">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" s="44"/>
-      <c r="C59" s="45" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="D59" s="45"/>
-      <c r="E59" s="45"/>
-      <c r="F59" s="46">
+      <c r="B60" s="45"/>
+      <c r="C60" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="47">
         <v>15.98</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="B60" s="47"/>
-      <c r="C60" s="48" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="D60" s="48"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="49">
+      <c r="B61" s="48"/>
+      <c r="C61" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" s="49"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="50">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="B61" s="44"/>
-      <c r="C61" s="45" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="45"/>
-      <c r="E61" s="45"/>
-      <c r="F61" s="50">
+      <c r="B62" s="45"/>
+      <c r="C62" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="D62" s="46"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="51">
         <v>3300</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="B62" s="47"/>
-      <c r="C62" s="48" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="D62" s="48"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="49">
+      <c r="B63" s="48"/>
+      <c r="C63" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="50">
         <v>52</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B63" s="44"/>
-      <c r="C63" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="D63" s="45"/>
-      <c r="E63" s="45"/>
-      <c r="F63" s="51">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" s="45"/>
+      <c r="C64" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="52">
         <v>82900</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="B64" s="47"/>
-      <c r="C64" s="48" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="D64" s="48"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="52">
+      <c r="B65" s="48"/>
+      <c r="C65" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="D65" s="49"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="53">
         <v>3729</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="B65" s="44"/>
-      <c r="C65" s="45" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="D65" s="45"/>
-      <c r="E65" s="45"/>
-      <c r="F65" s="51">
+      <c r="B66" s="45"/>
+      <c r="C66" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="52">
         <v>6760</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="47" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="48"/>
+      <c r="C67" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D67" s="49"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="53">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B68" s="45"/>
+      <c r="C68" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="D68" s="46"/>
+      <c r="E68" s="46"/>
+      <c r="F68" s="52">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="48"/>
+      <c r="C69" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="53">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70" s="45"/>
+      <c r="C70" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="46"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="52">
+        <v>5242.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="B66" s="47"/>
-      <c r="C66" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="D66" s="48"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="52">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="B67" s="44"/>
-      <c r="C67" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="D67" s="45"/>
-      <c r="E67" s="45"/>
-      <c r="F67" s="51">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="B68" s="47"/>
-      <c r="C68" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="52">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="B69" s="44"/>
-      <c r="C69" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="D69" s="45"/>
-      <c r="E69" s="45"/>
-      <c r="F69" s="51">
-        <v>5242.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="47"/>
-      <c r="C70" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="52">
+      <c r="B71" s="48"/>
+      <c r="C71" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="53">
         <v>10875</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="B71" s="44"/>
-      <c r="C71" s="45" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="51">
+      <c r="B72" s="45"/>
+      <c r="C72" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="52">
         <v>2024.1000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="B72" s="53"/>
-      <c r="C72" s="54" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="D72" s="54"/>
-      <c r="E72" s="54"/>
-      <c r="F72" s="55">
+      <c r="B73" s="54"/>
+      <c r="C73" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="56">
         <v>118780.6</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="B73" s="44"/>
-      <c r="C73" s="45" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="D73" s="45"/>
-      <c r="E73" s="45"/>
-      <c r="F73" s="51">
+      <c r="B74" s="45"/>
+      <c r="C74" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="D74" s="46"/>
+      <c r="E74" s="46"/>
+      <c r="F74" s="52">
         <v>712.9604778554778</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B74" s="47"/>
-      <c r="C74" s="48" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="52">
+      <c r="B75" s="48"/>
+      <c r="C75" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="53">
         <v>3717.08520979021</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="B75" s="44"/>
-      <c r="C75" s="45" t="s">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="D75" s="45"/>
-      <c r="E75" s="45"/>
-      <c r="F75" s="51">
+      <c r="B76" s="45"/>
+      <c r="C76" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D76" s="46"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="52">
         <v>15228.28205128205</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="47" t="s">
-        <v>108</v>
-      </c>
-      <c r="B76" s="47"/>
-      <c r="C76" s="48" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="52">
+      <c r="B77" s="48"/>
+      <c r="C77" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="D77" s="49"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="53">
         <v>18945.36726107226</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="B77" s="44"/>
-      <c r="C77" s="45" t="s">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="D77" s="45"/>
-      <c r="E77" s="45"/>
-      <c r="F77" s="51">
+      <c r="B78" s="45"/>
+      <c r="C78" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" s="46"/>
+      <c r="E78" s="46"/>
+      <c r="F78" s="52">
         <v>5297.175416550117</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="B78" s="53"/>
-      <c r="C78" s="54" t="s">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="D78" s="54"/>
-      <c r="E78" s="54"/>
-      <c r="F78" s="55">
+      <c r="B79" s="54"/>
+      <c r="C79" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D79" s="55"/>
+      <c r="E79" s="55"/>
+      <c r="F79" s="56">
         <v>143736.10315547785</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="B79" s="53"/>
-      <c r="C79" s="54" t="s">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="D79" s="54"/>
-      <c r="E79" s="54"/>
-      <c r="F79" s="55">
+      <c r="B80" s="54"/>
+      <c r="C80" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="D80" s="55"/>
+      <c r="E80" s="55"/>
+      <c r="F80" s="56">
         <v>124790.73589440559</v>
       </c>
     </row>
-    <row r="81" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="42" t="s">
+    <row r="82" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B82" s="42"/>
-      <c r="C82" s="43" t="s">
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="D82" s="43"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="B83" s="42"/>
-      <c r="C83" s="43" t="s">
+      <c r="B83" s="43"/>
+      <c r="C83" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="D83" s="44"/>
+      <c r="E83" s="44"/>
+      <c r="F83" s="44"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="D83" s="43"/>
-      <c r="E83" s="43"/>
-      <c r="F83" s="43"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="B84" s="42"/>
-      <c r="C84" s="43" t="s">
+      <c r="B84" s="43"/>
+      <c r="C84" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44"/>
+      <c r="F84" s="44"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="D84" s="43"/>
-      <c r="E84" s="43"/>
-      <c r="F84" s="43"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="42" t="s">
+      <c r="B85" s="43"/>
+      <c r="C85" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="B85" s="42"/>
-      <c r="C85" s="43" t="s">
+      <c r="D85" s="44"/>
+      <c r="E85" s="44"/>
+      <c r="F85" s="44"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="D85" s="43"/>
-      <c r="E85" s="43"/>
-      <c r="F85" s="43"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="42" t="s">
+      <c r="B86" s="43"/>
+      <c r="C86" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="B86" s="42"/>
-      <c r="C86" s="43" t="s">
+      <c r="D86" s="44"/>
+      <c r="E86" s="44"/>
+      <c r="F86" s="44"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="D86" s="43"/>
-      <c r="E86" s="43"/>
-      <c r="F86" s="43"/>
-    </row>
-    <row r="88" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="40" t="s">
+      <c r="B87" s="43"/>
+      <c r="C87" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="B88" s="40"/>
-      <c r="C88" s="40"/>
-      <c r="D88" s="40"/>
-      <c r="E88" s="40"/>
-      <c r="F88" s="40"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D87" s="44"/>
+      <c r="E87" s="44"/>
+      <c r="F87" s="44"/>
+    </row>
+    <row r="89" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="41" t="s">
         <v>126</v>
       </c>
@@ -2260,88 +2298,98 @@
       <c r="E89" s="41"/>
       <c r="F89" s="41"/>
     </row>
-    <row r="91" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="B91" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="C91" s="58" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="D91" s="58"/>
-      <c r="E91" s="58"/>
-      <c r="F91" s="57" t="s">
-        <v>31</v>
-      </c>
+      <c r="B90" s="42"/>
+      <c r="C90" s="42"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="42"/>
     </row>
     <row r="92" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="59" t="s">
+      <c r="A92" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="B92" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="B92" s="60">
+      <c r="D92" s="59"/>
+      <c r="E92" s="59"/>
+      <c r="F92" s="58" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="B93" s="61">
         <v>130</v>
       </c>
-      <c r="C92" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="D92" s="61"/>
-      <c r="E92" s="61"/>
-      <c r="F92" s="62" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="93" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="59" t="s">
+      <c r="C93" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="D93" s="62"/>
+      <c r="E93" s="62"/>
+      <c r="F93" s="63" t="s">
         <v>130</v>
       </c>
-      <c r="B93" s="60">
+    </row>
+    <row r="94" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B94" s="61">
         <v>45</v>
       </c>
-      <c r="C93" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D93" s="61"/>
-      <c r="E93" s="61"/>
-      <c r="F93" s="62" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="94" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="56" t="s">
+      <c r="C94" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="D94" s="62"/>
+      <c r="E94" s="62"/>
+      <c r="F94" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="B94" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="C94" s="61" t="s">
+    </row>
+    <row r="95" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="57" t="s">
         <v>133</v>
       </c>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="62" t="s">
+      <c r="B95" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="C95" s="62" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="95" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="59" t="s">
+      <c r="D95" s="62"/>
+      <c r="E95" s="62"/>
+      <c r="F95" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="B95" s="63" t="s">
+    </row>
+    <row r="96" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="C95" t="s">
-        <v>31</v>
-      </c>
-      <c r="D95"/>
-      <c r="E95"/>
-      <c r="F95" t="s">
-        <v>31</v>
+      <c r="B96" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="C96" t="s">
+        <v>32</v>
+      </c>
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="122">
+  <mergeCells count="123">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -2368,27 +2416,26 @@
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="D28:F28"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="C50:F50"/>
     <mergeCell ref="A51:B51"/>
@@ -2397,9 +2444,9 @@
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="C53:F53"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="C57:E57"/>
     <mergeCell ref="A58:B58"/>
@@ -2446,9 +2493,9 @@
     <mergeCell ref="C78:E78"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="C79:E79"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:F82"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A83:B83"/>
     <mergeCell ref="C83:F83"/>
     <mergeCell ref="A84:B84"/>
@@ -2457,22 +2504,24 @@
     <mergeCell ref="C85:F85"/>
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="C86:F86"/>
-    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C87:F87"/>
     <mergeCell ref="A89:F89"/>
-    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="A90:F90"/>
     <mergeCell ref="C92:E92"/>
     <mergeCell ref="C93:E93"/>
     <mergeCell ref="C94:E94"/>
     <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C96:E96"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="78" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="82" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8ul. Ogrodowa 8, Warszawa&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="44" max="16838" man="1"/>
-    <brk id="87" max="16838" man="1"/>
+    <brk id="45" max="16838" man="1"/>
+    <brk id="88" max="16838" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>